--- a/Team-Data/2012-13/4-4-2012-13.xlsx
+++ b/Team-Data/2012-13/4-4-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -748,7 +815,7 @@
         <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>11</v>
@@ -769,7 +836,7 @@
         <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
@@ -802,7 +869,7 @@
         <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
         <v>14</v>
@@ -939,7 +1006,7 @@
         <v>17</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>7</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" t="n">
         <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>0.573</v>
+        <v>0.581</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,7 +1110,7 @@
         <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>79.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0.448</v>
@@ -1052,7 +1119,7 @@
         <v>7.7</v>
       </c>
       <c r="M4" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="N4" t="n">
         <v>0.358</v>
@@ -1061,25 +1128,25 @@
         <v>17.4</v>
       </c>
       <c r="P4" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="R4" t="n">
         <v>12.7</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T4" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="U4" t="n">
         <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
@@ -1094,16 +1161,16 @@
         <v>18.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1121,7 +1188,7 @@
         <v>27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
         <v>16</v>
@@ -1136,7 +1203,7 @@
         <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
@@ -1148,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1163,10 +1230,10 @@
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
         <v>4</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1342,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>0.554</v>
+        <v>0.548</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
@@ -1425,10 +1492,10 @@
         <v>16.4</v>
       </c>
       <c r="P6" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="R6" t="n">
         <v>12.8</v>
@@ -1455,7 +1522,7 @@
         <v>5.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" t="n">
         <v>19.6</v>
@@ -1467,7 +1534,7 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1476,7 +1543,7 @@
         <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>15</v>
@@ -1506,7 +1573,7 @@
         <v>21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
         <v>5</v>
@@ -1518,16 +1585,16 @@
         <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX6" t="n">
         <v>11</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>12</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1539,7 +1606,7 @@
         <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
         <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>0.48</v>
+        <v>0.486</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
@@ -1774,25 +1841,25 @@
         <v>83.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M8" t="n">
         <v>20</v>
       </c>
       <c r="N8" t="n">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="O8" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P8" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R8" t="n">
         <v>9.199999999999999</v>
@@ -1804,7 +1871,7 @@
         <v>41.7</v>
       </c>
       <c r="U8" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
         <v>14.1</v>
@@ -1816,40 +1883,40 @@
         <v>5.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA8" t="n">
         <v>19.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>101</v>
+        <v>101.1</v>
       </c>
       <c r="AC8" t="n">
         <v>-1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK8" t="n">
         <v>9</v>
@@ -1864,10 +1931,10 @@
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1882,10 +1949,10 @@
         <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW8" t="n">
         <v>17</v>
@@ -1894,7 +1961,7 @@
         <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
         <v>23</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
         <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1956,13 +2023,13 @@
         <v>84.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L9" t="n">
         <v>6.3</v>
       </c>
       <c r="M9" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N9" t="n">
         <v>0.341</v>
@@ -1974,22 +2041,22 @@
         <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.699</v>
+        <v>0.7</v>
       </c>
       <c r="R9" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="S9" t="n">
         <v>31.4</v>
       </c>
       <c r="T9" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U9" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="V9" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W9" t="n">
         <v>9.199999999999999</v>
@@ -2007,13 +2074,13 @@
         <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="AC9" t="n">
         <v>4.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2082,7 +2149,7 @@
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2307,7 @@
         <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>0.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -2440,7 +2507,7 @@
         <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
@@ -2631,7 +2698,7 @@
         <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>5.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2753,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2810,7 +2877,7 @@
         <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2986,13 +3053,13 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ14" t="n">
         <v>25</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
@@ -3150,7 +3217,7 @@
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
         <v>3</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>17</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3484,7 +3551,7 @@
         <v>4</v>
       </c>
       <c r="AI17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3529,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3663,7 +3730,7 @@
         <v>17</v>
       </c>
       <c r="AH18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI18" t="n">
         <v>6</v>
@@ -3705,10 +3772,10 @@
         <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
@@ -3893,7 +3960,7 @@
         <v>11</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
         <v>24</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
@@ -4054,7 +4121,7 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
         <v>7</v>
@@ -4230,7 +4297,7 @@
         <v>6</v>
       </c>
       <c r="AO21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP21" t="n">
         <v>16</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F22" t="n">
         <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4325,19 +4392,19 @@
         <v>0.481</v>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M22" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.379</v>
+        <v>0.376</v>
       </c>
       <c r="O22" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="P22" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="Q22" t="n">
         <v>0.827</v>
@@ -4355,13 +4422,13 @@
         <v>21.5</v>
       </c>
       <c r="V22" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W22" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="Y22" t="n">
         <v>4</v>
@@ -4370,7 +4437,7 @@
         <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB22" t="n">
         <v>106</v>
@@ -4379,13 +4446,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
         <v>3</v>
@@ -4406,10 +4473,10 @@
         <v>13</v>
       </c>
       <c r="AM22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4424,10 +4491,10 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>21</v>
@@ -4436,7 +4503,7 @@
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4448,10 +4515,10 @@
         <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4655,7 @@
         <v>20</v>
       </c>
       <c r="AM23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN23" t="n">
         <v>28</v>
@@ -4615,7 +4682,7 @@
         <v>8</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4806,7 +4873,7 @@
         <v>19</v>
       </c>
       <c r="AY24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ24" t="n">
         <v>7</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,7 +5186,7 @@
         <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>18</v>
@@ -5155,13 +5222,13 @@
         <v>16</v>
       </c>
       <c r="AT26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU26" t="n">
         <v>19</v>
       </c>
       <c r="AV26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW26" t="n">
         <v>28</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,13 +5368,13 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>11</v>
       </c>
       <c r="AJ27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK27" t="n">
         <v>17</v>
@@ -5343,7 +5410,7 @@
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
         <v>13</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E28" t="n">
         <v>56</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>0.737</v>
+        <v>0.747</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="J28" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.484</v>
+        <v>0.486</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
@@ -5429,7 +5496,7 @@
         <v>16.7</v>
       </c>
       <c r="P28" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q28" t="n">
         <v>0.79</v>
@@ -5441,7 +5508,7 @@
         <v>33.1</v>
       </c>
       <c r="T28" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U28" t="n">
         <v>25.1</v>
@@ -5456,22 +5523,22 @@
         <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.5</v>
+        <v>103.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5519,13 +5586,13 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AW28" t="n">
         <v>5</v>
@@ -5534,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="AY28" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5686,7 +5753,7 @@
         <v>26</v>
       </c>
       <c r="AO29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5914,7 @@
         <v>16</v>
       </c>
       <c r="AH30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="n">
         <v>14</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
         <v>21</v>
@@ -6029,7 +6096,7 @@
         <v>22</v>
       </c>
       <c r="AH31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI31" t="n">
         <v>28</v>
@@ -6065,13 +6132,13 @@
         <v>6</v>
       </c>
       <c r="AT31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU31" t="n">
         <v>18</v>
       </c>
       <c r="AV31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
         <v>22</v>
@@ -6089,7 +6156,7 @@
         <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-4-2012-13</t>
+          <t>2013-04-04</t>
         </is>
       </c>
     </row>
